--- a/pynever/tests/movendo/data/SI_info.xlsx
+++ b/pynever/tests/movendo/data/SI_info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefa\Documents\Progetti\NeVerTools\pyNeVer\pynever\tests\movendo\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E3964D2-D61C-4A97-BDD6-E66556AA0F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{832F3C40-65AE-4A1C-A379-B891528A655A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{F1BBCDE2-4F84-444F-899D-0FA3D6AB17E4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{F1BBCDE2-4F84-444F-899D-0FA3D6AB17E4}"/>
   </bookViews>
   <sheets>
     <sheet name="RL_weights" sheetId="1" r:id="rId1"/>
@@ -1488,7 +1488,7 @@
         <v>0</v>
       </c>
       <c r="C32" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1852,7 +1852,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C32" s="13">
         <v>0</v>
